--- a/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
+++ b/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
@@ -11945,7 +11945,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
+++ b/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
@@ -11987,24 +11987,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sembrados: Z05 pierde actividad campaña a campaña mientras sube su orden promedio: la venta cae poco y eso esconde un problema serio de actividad;</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Z09 incorpora muchas asesoras nuevas pero su actividad cae (no se quedan). Un dato faltante de orden promedio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>La hoja de detalle sirve para practicar el semáforo: aunque tiene solo códigos, cruzarla con la base de asesoras la vuelve roja.</t>
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
+++ b/datasets/mp/02 Pedidos por zona y asesora - sintético.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen por zona" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle asesoras Z05 C10" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle asesoras (muestra)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LÉAME" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -11936,7 +11936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -11991,8 +11991,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
